--- a/artfynd/A 31357-2026 artfynd.xlsx
+++ b/artfynd/A 31357-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,27 +680,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135289434</v>
+        <v>136038667</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -711,7 +711,12 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -723,10 +728,10 @@
         <v>480141</v>
       </c>
       <c r="R2" t="n">
-        <v>6562155</v>
+        <v>6562223</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +755,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Multipla ringhack på tall</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,53 +781,1298 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136038667</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136038923</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lilla Motjärnen, Lilla Motjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>480202</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6562254</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136038923</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135289434</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lilla Motjärnen, Lilla Motjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>480141</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6562155</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Multipla ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135289434</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136037684</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lilla Motjärnen, Lilla Motjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>480144</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6562155</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136037684</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136039236</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lilla Motjärnen, Lilla Motjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>480242</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6562298</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska och äldre hack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136039236</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136038658</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lilla Motjärnen, Lilla Motjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>480144</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6562226</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136038658</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136038715</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lilla Motjärnen, Lilla Motjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>480130</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6562225</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Trolig spelspillning</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136038715</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136038770</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lilla Motjärnen, Lilla Motjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>480141</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6562225</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Vanlig och spelspillning</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136038770</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136038836</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lilla Motjärnen, Lilla Motjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>480150</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6562256</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136038836</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136039128</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lilla Motjärnen, Lilla Motjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>480189</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6562322</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136039128</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136038335</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58138</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lilla Motjärnen, Lilla Motjärnen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>480111</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6562192</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kvistbro</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136038335</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31357-2026 artfynd.xlsx
+++ b/artfynd/A 31357-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136038667</v>
       </c>
       <c r="B2" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136038923</v>
       </c>
       <c r="B3" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>136037684</v>
       </c>
       <c r="B5" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136039236</v>
       </c>
       <c r="B6" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136038658</v>
       </c>
       <c r="B7" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136038715</v>
       </c>
       <c r="B8" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>136038770</v>
       </c>
       <c r="B9" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136038836</v>
       </c>
       <c r="B10" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136039128</v>
       </c>
       <c r="B11" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>136038335</v>
       </c>
       <c r="B12" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31357-2026 artfynd.xlsx
+++ b/artfynd/A 31357-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136038667</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136038923</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>136037684</v>
       </c>
       <c r="B5" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136039236</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136038658</v>
       </c>
       <c r="B7" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136038715</v>
       </c>
       <c r="B8" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>136038770</v>
       </c>
       <c r="B9" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136038836</v>
       </c>
       <c r="B10" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136039128</v>
       </c>
       <c r="B11" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>136038335</v>
       </c>
       <c r="B12" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 31357-2026 artfynd.xlsx
+++ b/artfynd/A 31357-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136038667</v>
       </c>
       <c r="B2" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>136038923</v>
       </c>
       <c r="B3" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>136037684</v>
       </c>
       <c r="B5" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>136039236</v>
       </c>
       <c r="B6" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>136038658</v>
       </c>
       <c r="B7" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>136038715</v>
       </c>
       <c r="B8" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>136038770</v>
       </c>
       <c r="B9" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>136038836</v>
       </c>
       <c r="B10" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>136039128</v>
       </c>
       <c r="B11" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>136038335</v>
       </c>
       <c r="B12" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
